--- a/MLD01e_Results/Table52_AccuracyTable_CommunityPartipationPast25_v1.xlsx
+++ b/MLD01e_Results/Table52_AccuracyTable_CommunityPartipationPast25_v1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,28 +491,28 @@
         <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8565254969749352</v>
+        <v>0.867761452031115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7863013698630137</v>
+        <v>0.8100558659217877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7653333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7756756756756756</v>
+        <v>0.7912687585266031</v>
       </c>
       <c r="H2" t="n">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="I2" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K2" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8357821953327571</v>
+        <v>0.867761452031115</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7427821522309711</v>
+        <v>0.7890625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7546666666666667</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7486772486772487</v>
+        <v>0.7984189723320159</v>
       </c>
       <c r="H3" t="n">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="I3" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="J3" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>283</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8478824546240277</v>
+        <v>0.8617113223854796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7726027397260274</v>
+        <v>0.8062678062678063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.752</v>
+        <v>0.7546666666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7621621621621621</v>
+        <v>0.7796143250688705</v>
       </c>
       <c r="H4" t="n">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="I4" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8452895419187554</v>
+        <v>0.8608470181503889</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7598944591029023</v>
+        <v>0.7882037533512064</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7819148936170213</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7629139072847683</v>
+        <v>0.7850467289719626</v>
       </c>
       <c r="H5" t="n">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="I5" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J5" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8634399308556612</v>
+        <v>0.8712186689714779</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7898936170212766</v>
+        <v>0.814404432132964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7898936170212766</v>
+        <v>0.7819148936170213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7898936170212766</v>
+        <v>0.7978290366350068</v>
       </c>
       <c r="H6" t="n">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="J6" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8245462402765773</v>
+        <v>0.8478824546240277</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7258485639686684</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7393617021276596</v>
+        <v>0.7712765957446809</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7325428194993412</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="H7" t="n">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="I7" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="J7" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K7" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8340535868625756</v>
+        <v>0.8625756266205704</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7513661202185792</v>
+        <v>0.8091168091168092</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7313829787234043</v>
+        <v>0.7553191489361702</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7412398921832885</v>
+        <v>0.781292984869326</v>
       </c>
       <c r="H8" t="n">
-        <v>690</v>
+        <v>714</v>
       </c>
       <c r="I8" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="J8" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K8" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8556611927398444</v>
+        <v>0.878133102852204</v>
       </c>
       <c r="E9" t="n">
-        <v>0.784741144414169</v>
+        <v>0.8236914600550964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7952127659574468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.775235531628533</v>
+        <v>0.8092016238159675</v>
       </c>
       <c r="H9" t="n">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="I9" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="J9" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K9" t="n">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8434256055363322</v>
+        <v>0.8719723183391004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7621621621621621</v>
+        <v>0.810958904109589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7570469798657719</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="I10" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="J10" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K10" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>42</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8295847750865052</v>
+        <v>0.8598615916955017</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7418478260869565</v>
+        <v>0.7886178861788617</v>
       </c>
       <c r="F11" t="n">
-        <v>0.728</v>
+        <v>0.776</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7348586810228802</v>
+        <v>0.782258064516129</v>
       </c>
       <c r="H11" t="n">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="I11" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J11" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="K11" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8522039757994814</v>
+        <v>0.8634399308556612</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7642487046632125</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7752956636005256</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="I12" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K12" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8435609334485739</v>
+        <v>0.8582541054451167</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7755681818181818</v>
+        <v>0.8168168168168168</v>
       </c>
       <c r="F13" t="n">
-        <v>0.728</v>
+        <v>0.7253333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7510316368638239</v>
+        <v>0.768361581920904</v>
       </c>
       <c r="H13" t="n">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="I13" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="J13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K13" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8617113223854796</v>
+        <v>0.8720829732065687</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7763496143958869</v>
+        <v>0.7994722955145118</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8053333333333333</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7905759162303665</v>
+        <v>0.8037135278514589</v>
       </c>
       <c r="H14" t="n">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="I14" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K14" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>84</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8349178910976663</v>
+        <v>0.8573898012100259</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7329974811083123</v>
+        <v>0.772609819121447</v>
       </c>
       <c r="F15" t="n">
-        <v>0.773936170212766</v>
+        <v>0.7952127659574468</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7529107373868047</v>
+        <v>0.7837483617300131</v>
       </c>
       <c r="H15" t="n">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="I15" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J15" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K15" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>84</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8435609334485739</v>
+        <v>0.8608470181503889</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7656675749318801</v>
+        <v>0.7913279132791328</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7473404255319149</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="G16" t="n">
-        <v>0.756393001345895</v>
+        <v>0.7838926174496644</v>
       </c>
       <c r="H16" t="n">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="I16" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J16" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>84</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8608470181503889</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7928994082840237</v>
+        <v>0.8228228228228228</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7287234042553191</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7507002801120448</v>
+        <v>0.7729196050775741</v>
       </c>
       <c r="H17" t="n">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="I17" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K17" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>84</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8383751080380294</v>
+        <v>0.8617113223854796</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7617728531855956</v>
+        <v>0.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7313829787234043</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="G18" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="H18" t="n">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="I18" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J18" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K18" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>84</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8418323249783924</v>
+        <v>0.867761452031115</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7688022284122563</v>
+        <v>0.8140845070422535</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7510204081632653</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="H19" t="n">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="I19" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="K19" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>84</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8373702422145328</v>
+        <v>0.8512110726643599</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.7750677506775068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.7626666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.7688172043010753</v>
       </c>
       <c r="H20" t="n">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K20" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8503460207612457</v>
+        <v>0.8693771626297578</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7774725274725275</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7546666666666667</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7658998646820027</v>
+        <v>0.7967698519515478</v>
       </c>
       <c r="H21" t="n">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="I21" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J21" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K21" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>126</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8418323249783924</v>
+        <v>0.8556611927398444</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.8005780346820809</v>
       </c>
       <c r="F22" t="n">
-        <v>0.72</v>
+        <v>0.7386666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7468879668049793</v>
+        <v>0.768377253814147</v>
       </c>
       <c r="H22" t="n">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="I22" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J22" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K22" t="n">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8297320656871219</v>
+        <v>0.8634399308556612</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7418478260869565</v>
+        <v>0.7956403269754768</v>
       </c>
       <c r="F23" t="n">
-        <v>0.728</v>
+        <v>0.7786666666666666</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7348586810228802</v>
+        <v>0.7870619946091644</v>
       </c>
       <c r="H23" t="n">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="I23" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J23" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>126</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8591184096802075</v>
+        <v>0.8694900605012964</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7789473684210526</v>
+        <v>0.7994652406417112</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7893333333333333</v>
+        <v>0.7973333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7841059602649006</v>
+        <v>0.7983978638184246</v>
       </c>
       <c r="H24" t="n">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="I24" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J24" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K24" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>126</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8271391529818496</v>
+        <v>0.8522039757994814</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7313829787234043</v>
+        <v>0.7632978723404256</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7704697986577181</v>
       </c>
       <c r="H25" t="n">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="I25" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="J25" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="K25" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>126</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.8703543647363872</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7539267015706806</v>
+        <v>0.8104395604395604</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7845744680851063</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7598944591029023</v>
+        <v>0.7972972972972973</v>
       </c>
       <c r="H26" t="n">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="I26" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="J26" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K26" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>126</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8357821953327571</v>
+        <v>0.8496110630942092</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7790055248618785</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.75</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7382920110192838</v>
+        <v>0.7642276422764228</v>
       </c>
       <c r="H27" t="n">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I27" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J27" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="K27" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>126</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8487467588591184</v>
+        <v>0.8582541054451167</v>
       </c>
       <c r="E28" t="n">
-        <v>0.762402088772846</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="F28" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="G28" t="n">
-        <v>0.769433465085639</v>
+        <v>0.783068783068783</v>
       </c>
       <c r="H28" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="I28" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K28" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>126</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8599827139152982</v>
+        <v>0.8686257562662058</v>
       </c>
       <c r="E29" t="n">
-        <v>0.800561797752809</v>
+        <v>0.8163841807909604</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7579787234042553</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7786885245901639</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="H29" t="n">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="I29" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J29" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K29" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>126</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8503460207612457</v>
+        <v>0.8719723183391004</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7603092783505154</v>
+        <v>0.7979002624671916</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8106666666666666</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7732634338138925</v>
+        <v>0.8042328042328042</v>
       </c>
       <c r="H30" t="n">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="I30" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J30" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K30" t="n">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>126</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8347750865051903</v>
+        <v>0.8494809688581315</v>
       </c>
       <c r="E31" t="n">
-        <v>0.75</v>
+        <v>0.7723577235772358</v>
       </c>
       <c r="F31" t="n">
-        <v>0.736</v>
+        <v>0.76</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7429340511440108</v>
+        <v>0.7661290322580645</v>
       </c>
       <c r="H31" t="n">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="I31" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J31" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K31" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>168</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8331892826274849</v>
+        <v>0.8591184096802075</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7420212765957447</v>
+        <v>0.7864864864864864</v>
       </c>
       <c r="F32" t="n">
-        <v>0.744</v>
+        <v>0.776</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7430093209054593</v>
+        <v>0.7812080536912752</v>
       </c>
       <c r="H32" t="n">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="I32" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J32" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K32" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>168</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8254105445116681</v>
+        <v>0.8522039757994814</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7331536388140162</v>
+        <v>0.7771739130434783</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7253333333333334</v>
+        <v>0.7626666666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7292225201072386</v>
+        <v>0.7698519515477793</v>
       </c>
       <c r="H33" t="n">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="I33" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="J33" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K33" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>168</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8470181503889369</v>
+        <v>0.8643042350907519</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.793010752688172</v>
       </c>
       <c r="F34" t="n">
-        <v>0.768</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7649402390438247</v>
+        <v>0.7898259705488622</v>
       </c>
       <c r="H34" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="I34" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J34" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K34" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>168</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8573898012100259</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7605263157894737</v>
+        <v>0.7890410958904109</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7686170212765957</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7645502645502645</v>
+        <v>0.7773279352226721</v>
       </c>
       <c r="H35" t="n">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="I35" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J35" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>168</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8530682800345721</v>
+        <v>0.8582541054451167</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7768817204301075</v>
+        <v>0.7994350282485876</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7686170212765957</v>
+        <v>0.7526595744680851</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7753424657534247</v>
       </c>
       <c r="H36" t="n">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="I36" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="J36" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K36" t="n">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>168</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8366464995678479</v>
+        <v>0.8608470181503889</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7710144927536232</v>
+        <v>0.8097982708933718</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7074468085106383</v>
+        <v>0.7473404255319149</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.7773167358229599</v>
       </c>
       <c r="H37" t="n">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="I37" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="J37" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="K37" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>168</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8547968885047537</v>
+        <v>0.867761452031115</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7841530054644809</v>
+        <v>0.8021680216802168</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7632978723404256</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7946308724832215</v>
       </c>
       <c r="H38" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="I38" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J38" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K38" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>168</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8254105445116681</v>
+        <v>0.8530682800345721</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7338709677419355</v>
+        <v>0.7877094972067039</v>
       </c>
       <c r="F39" t="n">
-        <v>0.726063829787234</v>
+        <v>0.75</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7299465240641712</v>
+        <v>0.7683923705722071</v>
       </c>
       <c r="H39" t="n">
-        <v>682</v>
+        <v>705</v>
       </c>
       <c r="I39" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="J39" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="K39" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>168</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8711072664359861</v>
+        <v>0.8814878892733564</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8104395604395604</v>
+        <v>0.8216216216216217</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8106666666666666</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7983761840324763</v>
+        <v>0.8161073825503355</v>
       </c>
       <c r="H40" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="I40" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J40" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>168</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8451557093425606</v>
+        <v>0.8745674740484429</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7578947368421053</v>
+        <v>0.8125</v>
       </c>
       <c r="F41" t="n">
-        <v>0.768</v>
+        <v>0.7973333333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7629139072847683</v>
+        <v>0.8048452220726783</v>
       </c>
       <c r="H41" t="n">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="I41" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="J41" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>210</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.867761452031115</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7749287749287749</v>
+        <v>0.8153409090909091</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7253333333333334</v>
+        <v>0.7653333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7493112947658402</v>
+        <v>0.7895460797799174</v>
       </c>
       <c r="H42" t="n">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="I42" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="J42" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="K42" t="n">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>210</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8496110630942092</v>
+        <v>0.8591184096802075</v>
       </c>
       <c r="E43" t="n">
-        <v>0.778393351800554</v>
+        <v>0.7896174863387978</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.7706666666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7635869565217391</v>
+        <v>0.7800269905533064</v>
       </c>
       <c r="H43" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="I43" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J43" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K43" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>210</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8366464995678479</v>
+        <v>0.8504753673293</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7473404255319149</v>
+        <v>0.7744565217391305</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.76</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7483355525965379</v>
+        <v>0.7671601615074024</v>
       </c>
       <c r="H44" t="n">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="I44" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J44" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>210</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8401037165082109</v>
+        <v>0.8513396715643907</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7442455242966752</v>
+        <v>0.7642487046632125</v>
       </c>
       <c r="F45" t="n">
-        <v>0.773936170212766</v>
+        <v>0.7845744680851063</v>
       </c>
       <c r="G45" t="n">
-        <v>0.758800521512386</v>
+        <v>0.7742782152230971</v>
       </c>
       <c r="H45" t="n">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J45" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K45" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>210</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8323249783923942</v>
+        <v>0.8660328435609335</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7570621468926554</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7606382978723404</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7342465753424657</v>
+        <v>0.7867950481430537</v>
       </c>
       <c r="H46" t="n">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="I46" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="J46" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K46" t="n">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>210</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8513396715643907</v>
+        <v>0.8660328435609335</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7670157068062827</v>
+        <v>0.8077994428969359</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7792553191489362</v>
+        <v>0.7712765957446809</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7730870712401056</v>
+        <v>0.7891156462585034</v>
       </c>
       <c r="H47" t="n">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="I47" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="J47" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K47" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>210</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8539325842696629</v>
+        <v>0.8643042350907519</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.8050139275766016</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7731543624161074</v>
+        <v>0.7863945578231293</v>
       </c>
       <c r="H48" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="I48" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="J48" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K48" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49">
@@ -2136,22 +2136,22 @@
         <v>210</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8470181503889369</v>
+        <v>0.8582541054451167</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7726027397260274</v>
+        <v>0.8011363636363636</v>
       </c>
       <c r="F49" t="n">
         <v>0.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7611336032388664</v>
+        <v>0.7747252747252747</v>
       </c>
       <c r="H49" t="n">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="I49" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J49" t="n">
         <v>94</v>
@@ -2171,28 +2171,28 @@
         <v>210</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8520761245674741</v>
+        <v>0.8711072664359861</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7817679558011049</v>
+        <v>0.8174157303370787</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7546666666666667</v>
+        <v>0.776</v>
       </c>
       <c r="G50" t="n">
-        <v>0.76797829036635</v>
+        <v>0.7961696306429549</v>
       </c>
       <c r="H50" t="n">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="I50" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="J50" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K50" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51">
@@ -2206,28 +2206,28 @@
         <v>210</v>
       </c>
       <c r="D51" t="n">
-        <v>0.828719723183391</v>
+        <v>0.856401384083045</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7310704960835509</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.792</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7387862796833773</v>
+        <v>0.781578947368421</v>
       </c>
       <c r="H51" t="n">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="I51" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="J51" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K51" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52">
@@ -2241,28 +2241,28 @@
         <v>252</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8383751080380294</v>
+        <v>0.8573898012100259</v>
       </c>
       <c r="E52" t="n">
-        <v>0.754054054054054</v>
+        <v>0.7949438202247191</v>
       </c>
       <c r="F52" t="n">
-        <v>0.744</v>
+        <v>0.7546666666666667</v>
       </c>
       <c r="G52" t="n">
-        <v>0.748993288590604</v>
+        <v>0.7742818057455541</v>
       </c>
       <c r="H52" t="n">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="I52" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="J52" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K52" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53">
@@ -2276,28 +2276,28 @@
         <v>252</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8141745894554884</v>
+        <v>0.8556611927398444</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.7872928176795581</v>
       </c>
       <c r="F53" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7152317880794702</v>
+        <v>0.7734056987788331</v>
       </c>
       <c r="H53" t="n">
-        <v>672</v>
+        <v>705</v>
       </c>
       <c r="I53" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="J53" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="K53" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54">
@@ -2311,28 +2311,28 @@
         <v>252</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8435609334485739</v>
+        <v>0.8608470181503889</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7664835164835165</v>
+        <v>0.7939560439560439</v>
       </c>
       <c r="F54" t="n">
-        <v>0.744</v>
+        <v>0.7706666666666667</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7550744248985115</v>
+        <v>0.7821380243572396</v>
       </c>
       <c r="H54" t="n">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="I54" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J54" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="K54" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55">
@@ -2346,28 +2346,28 @@
         <v>252</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8556611927398444</v>
+        <v>0.8660328435609335</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7659033078880407</v>
+        <v>0.779746835443038</v>
       </c>
       <c r="F55" t="n">
-        <v>0.800531914893617</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7828348504551366</v>
+        <v>0.7989623865110247</v>
       </c>
       <c r="H55" t="n">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="I55" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J55" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K55" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56">
@@ -2381,28 +2381,28 @@
         <v>252</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8487467588591184</v>
+        <v>0.878133102852204</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7723577235772358</v>
+        <v>0.8116710875331565</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7579787234042553</v>
+        <v>0.8138297872340425</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7651006711409396</v>
+        <v>0.8127490039840638</v>
       </c>
       <c r="H56" t="n">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="I56" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="J56" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="K56" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57">
@@ -2416,28 +2416,28 @@
         <v>252</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8418323249783924</v>
+        <v>0.8556611927398444</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7749287749287749</v>
+        <v>0.7927170868347339</v>
       </c>
       <c r="F57" t="n">
-        <v>0.723404255319149</v>
+        <v>0.7526595744680851</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7482806052269602</v>
+        <v>0.7721691678035471</v>
       </c>
       <c r="H57" t="n">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="I57" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J57" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K57" t="n">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58">
@@ -2451,28 +2451,28 @@
         <v>252</v>
       </c>
       <c r="D58" t="n">
-        <v>0.8547968885047537</v>
+        <v>0.8729472774416595</v>
       </c>
       <c r="E58" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8189415041782729</v>
       </c>
       <c r="F58" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7819148936170213</v>
       </c>
       <c r="G58" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8</v>
       </c>
       <c r="H58" t="n">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="I58" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="J58" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K58" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59">
@@ -2486,28 +2486,28 @@
         <v>252</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8357821953327571</v>
+        <v>0.8591184096802075</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7527173913043478</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7367021276595744</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7446236559139785</v>
+        <v>0.7800269905533064</v>
       </c>
       <c r="H59" t="n">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="I59" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J59" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K59" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60">
@@ -2521,28 +2521,28 @@
         <v>252</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8373702422145328</v>
+        <v>0.8460207612456747</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7669376693766937</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7626666666666667</v>
+        <v>0.7546666666666667</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7526315789473684</v>
+        <v>0.760752688172043</v>
       </c>
       <c r="H60" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="I60" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="J60" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K60" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61">
@@ -2556,28 +2556,28 @@
         <v>252</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8520761245674741</v>
+        <v>0.8650519031141869</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7865168539325843</v>
+        <v>0.8137535816618912</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7573333333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7660738714090287</v>
+        <v>0.7845303867403315</v>
       </c>
       <c r="H61" t="n">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="I61" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J61" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K61" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62">
@@ -2591,28 +2591,28 @@
         <v>294</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8608470181503889</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7923497267759563</v>
+        <v>0.8135135135135135</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8026666666666666</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7827260458839406</v>
+        <v>0.8080536912751678</v>
       </c>
       <c r="H62" t="n">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="I62" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J62" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63">
@@ -2626,28 +2626,28 @@
         <v>294</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8435609334485739</v>
+        <v>0.8634399308556612</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7566137566137566</v>
+        <v>0.7803617571059431</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7626666666666667</v>
+        <v>0.8053333333333333</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7596281540504648</v>
+        <v>0.7926509186351706</v>
       </c>
       <c r="H63" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="I63" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J63" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="K63" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64">
@@ -2661,28 +2661,28 @@
         <v>294</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8530682800345721</v>
+        <v>0.8703543647363872</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7855153203342619</v>
+        <v>0.8082191780821918</v>
       </c>
       <c r="F64" t="n">
-        <v>0.752</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7683923705722071</v>
+        <v>0.7972972972972973</v>
       </c>
       <c r="H64" t="n">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="I64" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J64" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K64" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65">
@@ -2696,28 +2696,28 @@
         <v>294</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8573898012100259</v>
+        <v>0.8772687986171133</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7874659400544959</v>
+        <v>0.8232044198895028</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7686170212765957</v>
+        <v>0.7925531914893617</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7779273216689099</v>
+        <v>0.8075880758807588</v>
       </c>
       <c r="H65" t="n">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="I65" t="n">
+        <v>64</v>
+      </c>
+      <c r="J65" t="n">
         <v>78</v>
       </c>
-      <c r="J65" t="n">
-        <v>87</v>
-      </c>
       <c r="K65" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="66">
@@ -2731,28 +2731,28 @@
         <v>294</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8340535868625756</v>
+        <v>0.8530682800345721</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7459893048128342</v>
+        <v>0.7724867724867724</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7420212765957447</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="G66" t="n">
-        <v>0.744</v>
+        <v>0.7745358090185677</v>
       </c>
       <c r="H66" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="I66" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J66" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K66" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67">
@@ -2766,28 +2766,28 @@
         <v>294</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8383751080380294</v>
+        <v>0.8530682800345721</v>
       </c>
       <c r="E67" t="n">
-        <v>0.7467362924281984</v>
+        <v>0.7877094972067039</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7606382978723404</v>
+        <v>0.75</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7536231884057971</v>
+        <v>0.7683923705722071</v>
       </c>
       <c r="H67" t="n">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="I67" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J67" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K67" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="68">
@@ -2801,28 +2801,28 @@
         <v>294</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8228176318063959</v>
+        <v>0.8522039757994814</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7342465753424657</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7233468286099866</v>
+        <v>0.7660738714090287</v>
       </c>
       <c r="H68" t="n">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="I68" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="J68" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K68" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69">
@@ -2836,28 +2836,28 @@
         <v>294</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8392394122731202</v>
+        <v>0.8487467588591184</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7540106951871658</v>
+        <v>0.7830985915492957</v>
       </c>
       <c r="F69" t="n">
-        <v>0.75</v>
+        <v>0.7393617021276596</v>
       </c>
       <c r="G69" t="n">
-        <v>0.752</v>
+        <v>0.7606019151846786</v>
       </c>
       <c r="H69" t="n">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="I69" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J69" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K69" t="n">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70">
@@ -2871,28 +2871,28 @@
         <v>294</v>
       </c>
       <c r="D70" t="n">
-        <v>0.846885813148789</v>
+        <v>0.8633217993079585</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.8144927536231884</v>
       </c>
       <c r="F70" t="n">
-        <v>0.736</v>
+        <v>0.7493333333333333</v>
       </c>
       <c r="G70" t="n">
-        <v>0.757201646090535</v>
+        <v>0.7805555555555556</v>
       </c>
       <c r="H70" t="n">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="I70" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="J70" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K70" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71">
@@ -2906,28 +2906,28 @@
         <v>294</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8503460207612457</v>
+        <v>0.8685121107266436</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7671957671957672</v>
+        <v>0.8054794520547945</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.784</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7702523240371846</v>
+        <v>0.7945945945945946</v>
       </c>
       <c r="H71" t="n">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="I71" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="J71" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K71" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72">
@@ -2941,28 +2941,28 @@
         <v>336</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8375108038029386</v>
+        <v>0.8729472774416595</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7561643835616438</v>
+        <v>0.8202247191011236</v>
       </c>
       <c r="F72" t="n">
-        <v>0.736</v>
+        <v>0.7786666666666666</v>
       </c>
       <c r="G72" t="n">
-        <v>0.745945945945946</v>
+        <v>0.7989056087551299</v>
       </c>
       <c r="H72" t="n">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="I72" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="J72" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K72" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73">
@@ -2976,28 +2976,28 @@
         <v>336</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8539325842696629</v>
+        <v>0.8755401901469317</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7768817204301075</v>
+        <v>0.8130081300813008</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7706666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="G73" t="n">
-        <v>0.7737617135207496</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="H73" t="n">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="I73" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J73" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K73" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74">
@@ -3011,28 +3011,28 @@
         <v>336</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8305963699222126</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7312661498708011</v>
+        <v>0.7532133676092545</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7546666666666667</v>
+        <v>0.7813333333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7427821522309711</v>
+        <v>0.7670157068062827</v>
       </c>
       <c r="H74" t="n">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="I74" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="J74" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K74" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75">
@@ -3046,28 +3046,28 @@
         <v>336</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8504753673293</v>
+        <v>0.8625756266205704</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7582697201017812</v>
+        <v>0.7893333333333333</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7925531914893617</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7750325097529259</v>
+        <v>0.7882822902796272</v>
       </c>
       <c r="H75" t="n">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="I75" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="J75" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K75" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="76">
@@ -3081,28 +3081,28 @@
         <v>336</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8522039757994814</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="E76" t="n">
-        <v>0.774798927613941</v>
+        <v>0.8245125348189415</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7686170212765957</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7716955941255007</v>
+        <v>0.8054421768707483</v>
       </c>
       <c r="H76" t="n">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="I76" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="J76" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K76" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="77">
@@ -3116,28 +3116,28 @@
         <v>336</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8314606741573034</v>
+        <v>0.8444252376836646</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7578347578347578</v>
+        <v>0.7768361581920904</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7074468085106383</v>
+        <v>0.7313829787234043</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7317744154057771</v>
+        <v>0.7534246575342466</v>
       </c>
       <c r="H77" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="I77" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J77" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K77" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78">
@@ -3151,28 +3151,28 @@
         <v>336</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8297320656871219</v>
+        <v>0.8452895419187554</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7412398921832885</v>
+        <v>0.7612732095490716</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7313829787234043</v>
+        <v>0.7632978723404256</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7362784471218207</v>
+        <v>0.7622841965471447</v>
       </c>
       <c r="H78" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="I78" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J78" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="K78" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="79">
@@ -3186,28 +3186,28 @@
         <v>336</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8530682800345721</v>
+        <v>0.8582541054451167</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7783783783783784</v>
+        <v>0.7960893854748603</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7579787234042553</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7721179624664879</v>
+        <v>0.776566757493188</v>
       </c>
       <c r="H79" t="n">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="I79" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J79" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K79" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80">
@@ -3221,28 +3221,28 @@
         <v>336</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8416955017301038</v>
+        <v>0.8728373702422145</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.8015873015873016</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7537012113055181</v>
+        <v>0.8047808764940239</v>
       </c>
       <c r="H80" t="n">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="I80" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J80" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="K80" t="n">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81">
@@ -3256,28 +3256,28 @@
         <v>336</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8408304498269896</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7645429362880887</v>
+        <v>0.7855153203342619</v>
       </c>
       <c r="F81" t="n">
-        <v>0.736</v>
+        <v>0.752</v>
       </c>
       <c r="G81" t="n">
-        <v>0.75</v>
+        <v>0.7683923705722071</v>
       </c>
       <c r="H81" t="n">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="I81" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J81" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K81" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82">
@@ -3291,28 +3291,28 @@
         <v>378</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8444252376836646</v>
+        <v>0.8591184096802075</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7656675749318801</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7493333333333333</v>
+        <v>0.7786666666666666</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7574123989218329</v>
+        <v>0.7817938420348058</v>
       </c>
       <c r="H82" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="I82" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J82" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K82" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="83">
@@ -3326,28 +3326,28 @@
         <v>378</v>
       </c>
       <c r="D83" t="n">
-        <v>0.8392394122731202</v>
+        <v>0.8651685393258427</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7632311977715878</v>
+        <v>0.8033240997229917</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7306666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7465940054495913</v>
+        <v>0.7880434782608695</v>
       </c>
       <c r="H83" t="n">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="I83" t="n">
+        <v>71</v>
+      </c>
+      <c r="J83" t="n">
         <v>85</v>
       </c>
-      <c r="J83" t="n">
-        <v>101</v>
-      </c>
       <c r="K83" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="84">
@@ -3361,28 +3361,28 @@
         <v>378</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8582541054451167</v>
+        <v>0.878133102852204</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7798408488063661</v>
+        <v>0.8286516853932584</v>
       </c>
       <c r="F84" t="n">
-        <v>0.784</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7819148936170213</v>
+        <v>0.8071135430916553</v>
       </c>
       <c r="H84" t="n">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="I84" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="J84" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K84" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85">
@@ -3396,28 +3396,28 @@
         <v>378</v>
       </c>
       <c r="D85" t="n">
-        <v>0.8280034572169404</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7286821705426356</v>
+        <v>0.7716535433070866</v>
       </c>
       <c r="F85" t="n">
-        <v>0.75</v>
+        <v>0.7819148936170213</v>
       </c>
       <c r="G85" t="n">
-        <v>0.7391874180865007</v>
+        <v>0.7767503302509907</v>
       </c>
       <c r="H85" t="n">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="I85" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="J85" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
     </row>
     <row r="86">
@@ -3431,28 +3431,28 @@
         <v>378</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8349178910976663</v>
+        <v>0.8591184096802075</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7479892761394102</v>
+        <v>0.7917808219178082</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7420212765957447</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G86" t="n">
-        <v>0.7449933244325768</v>
+        <v>0.7800269905533064</v>
       </c>
       <c r="H86" t="n">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="I86" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J86" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K86" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="87">
@@ -3466,28 +3466,28 @@
         <v>378</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8349178910976663</v>
+        <v>0.8599827139152982</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7365728900255755</v>
+        <v>0.7845744680851063</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7845744680851063</v>
       </c>
       <c r="G87" t="n">
-        <v>0.7509778357235984</v>
+        <v>0.7845744680851063</v>
       </c>
       <c r="H87" t="n">
-        <v>678</v>
+        <v>700</v>
       </c>
       <c r="I87" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="J87" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K87" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88">
@@ -3501,28 +3501,28 @@
         <v>378</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8565254969749352</v>
+        <v>0.8729472774416595</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7932960893854749</v>
+        <v>0.8225352112676056</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="G88" t="n">
-        <v>0.773841961852861</v>
+        <v>0.7989056087551299</v>
       </c>
       <c r="H88" t="n">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="I88" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="J88" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K88" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89">
@@ -3536,28 +3536,28 @@
         <v>378</v>
       </c>
       <c r="D89" t="n">
-        <v>0.8323249783923942</v>
+        <v>0.8496110630942092</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7570621468926554</v>
+        <v>0.7821229050279329</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="G89" t="n">
-        <v>0.7342465753424657</v>
+        <v>0.7629427792915532</v>
       </c>
       <c r="H89" t="n">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="I89" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J89" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K89" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90">
@@ -3571,28 +3571,28 @@
         <v>378</v>
       </c>
       <c r="D90" t="n">
-        <v>0.8555363321799307</v>
+        <v>0.8693771626297578</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7905027932960894</v>
+        <v>0.8128491620111732</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7546666666666667</v>
+        <v>0.776</v>
       </c>
       <c r="G90" t="n">
-        <v>0.7721691678035471</v>
+        <v>0.7939972714870396</v>
       </c>
       <c r="H90" t="n">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I90" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J90" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K90" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91">
@@ -3606,28 +3606,28 @@
         <v>378</v>
       </c>
       <c r="D91" t="n">
-        <v>0.8512110726643599</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.8292011019283747</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7653333333333333</v>
+        <v>0.8026666666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0.7694369973190348</v>
+        <v>0.8157181571815718</v>
       </c>
       <c r="H91" t="n">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="I91" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="J91" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="K91" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92">
@@ -3641,28 +3641,28 @@
         <v>420</v>
       </c>
       <c r="D92" t="n">
-        <v>0.8401037165082109</v>
+        <v>0.8409680207433017</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7595628415300546</v>
+        <v>0.7630853994490359</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7413333333333333</v>
+        <v>0.7386666666666667</v>
       </c>
       <c r="G92" t="n">
-        <v>0.7503373819163293</v>
+        <v>0.7506775067750677</v>
       </c>
       <c r="H92" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I92" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J92" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K92" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93">
@@ -3676,22 +3676,22 @@
         <v>420</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8409680207433017</v>
+        <v>0.8513396715643907</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7519788918205804</v>
+        <v>0.776566757493188</v>
       </c>
       <c r="F93" t="n">
         <v>0.76</v>
       </c>
       <c r="G93" t="n">
-        <v>0.7559681697612732</v>
+        <v>0.7681940700808625</v>
       </c>
       <c r="H93" t="n">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="I93" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J93" t="n">
         <v>90</v>
@@ -3711,28 +3711,28 @@
         <v>420</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8547968885047537</v>
+        <v>0.8703543647363872</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.8016085790884718</v>
       </c>
       <c r="F94" t="n">
-        <v>0.768</v>
+        <v>0.7973333333333333</v>
       </c>
       <c r="G94" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7994652406417112</v>
       </c>
       <c r="H94" t="n">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="I94" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J94" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K94" t="n">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="95">
@@ -3746,28 +3746,28 @@
         <v>420</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8375108038029386</v>
+        <v>0.8617113223854796</v>
       </c>
       <c r="E95" t="n">
-        <v>0.75</v>
+        <v>0.7983425414364641</v>
       </c>
       <c r="F95" t="n">
-        <v>0.75</v>
+        <v>0.7686170212765957</v>
       </c>
       <c r="G95" t="n">
-        <v>0.75</v>
+        <v>0.7831978319783198</v>
       </c>
       <c r="H95" t="n">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="I95" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="J95" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K95" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96">
@@ -3781,28 +3781,28 @@
         <v>420</v>
       </c>
       <c r="D96" t="n">
-        <v>0.8547968885047537</v>
+        <v>0.8807260155574762</v>
       </c>
       <c r="E96" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8233695652173914</v>
       </c>
       <c r="F96" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8058510638297872</v>
       </c>
       <c r="G96" t="n">
-        <v>0.776595744680851</v>
+        <v>0.8145161290322581</v>
       </c>
       <c r="H96" t="n">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="I96" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="J96" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="K96" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="97">
@@ -3816,28 +3816,28 @@
         <v>420</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8556611927398444</v>
+        <v>0.8738115816767502</v>
       </c>
       <c r="E97" t="n">
-        <v>0.784741144414169</v>
+        <v>0.8142076502732241</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7925531914893617</v>
       </c>
       <c r="G97" t="n">
-        <v>0.775235531628533</v>
+        <v>0.8032345013477089</v>
       </c>
       <c r="H97" t="n">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="I97" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="J97" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K97" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="98">
@@ -3851,28 +3851,28 @@
         <v>420</v>
       </c>
       <c r="D98" t="n">
-        <v>0.8340535868625756</v>
+        <v>0.8496110630942092</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7459893048128342</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7420212765957447</v>
+        <v>0.7712765957446809</v>
       </c>
       <c r="G98" t="n">
-        <v>0.744</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="H98" t="n">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="I98" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J98" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K98" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99">
@@ -3886,28 +3886,28 @@
         <v>420</v>
       </c>
       <c r="D99" t="n">
-        <v>0.8504753673293</v>
+        <v>0.8668971477960242</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7780821917808219</v>
+        <v>0.8066298342541437</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="G99" t="n">
-        <v>0.766531713900135</v>
+        <v>0.7913279132791328</v>
       </c>
       <c r="H99" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="I99" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="J99" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K99" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="100">
@@ -3921,28 +3921,28 @@
         <v>420</v>
       </c>
       <c r="D100" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8434256055363322</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7255936675461742</v>
+        <v>0.7635869565217391</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7493333333333333</v>
       </c>
       <c r="G100" t="n">
-        <v>0.7294429708222812</v>
+        <v>0.756393001345895</v>
       </c>
       <c r="H100" t="n">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="I100" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K100" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="101">
@@ -3956,28 +3956,28 @@
         <v>420</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8391003460207612</v>
+        <v>0.8650519031141869</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7574931880108992</v>
+        <v>0.8101983002832861</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7413333333333333</v>
+        <v>0.7626666666666667</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7493261455525606</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="H101" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="I101" t="n">
+        <v>67</v>
+      </c>
+      <c r="J101" t="n">
         <v>89</v>
       </c>
-      <c r="J101" t="n">
-        <v>97</v>
-      </c>
       <c r="K101" t="n">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
